--- a/data/user/user.xlsx
+++ b/data/user/user.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6092218aa314deb/Dokumente/hackerthon/data/user/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{C74F6FAA-9F9A-4FC4-BE34-46D1A99E7820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8373364E-7D90-4B54-B8BB-4BF4071AD107}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{C74F6FAA-9F9A-4FC4-BE34-46D1A99E7820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A8916C7-DDB8-427A-9FB0-49682C48C13B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" xr2:uid="{D427C77A-E679-44B6-86BB-64B55F7FE4CF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" activeTab="1" xr2:uid="{D427C77A-E679-44B6-86BB-64B55F7FE4CF}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="5" r:id="rId1"/>
-    <sheet name="health_data" sheetId="6" r:id="rId2"/>
+    <sheet name="profile" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>user_name</t>
   </si>
@@ -57,40 +57,28 @@
     <t>phone</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>admin@outlook.de</t>
-  </si>
-  <si>
     <t>contry</t>
   </si>
   <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>admin_u</t>
-  </si>
-  <si>
     <t>sessionid</t>
   </si>
   <si>
-    <t>health_integer</t>
-  </si>
-  <si>
-    <t>effecency_intiger</t>
-  </si>
-  <si>
-    <t>curve_total_health</t>
-  </si>
-  <si>
-    <t>curve_sleep_health</t>
-  </si>
-  <si>
-    <t>curve_food_health</t>
-  </si>
-  <si>
-    <t>curve_activity_health</t>
+    <t>health_float</t>
+  </si>
+  <si>
+    <t>health_curve</t>
+  </si>
+  <si>
+    <t>sleep_curve</t>
+  </si>
+  <si>
+    <t>food_curve</t>
+  </si>
+  <si>
+    <t>act_curve</t>
+  </si>
+  <si>
+    <t>gen_profile</t>
   </si>
 </sst>
 </file>
@@ -499,7 +487,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -514,36 +502,13 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
-        <v>1234</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>123123444</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
+      <c r="E2" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{98854BE6-B911-4622-85BF-180A7A4739C9}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -553,9 +518,9 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.7265625" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
-    <col min="4" max="4" width="27.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" customWidth="1"/>
+    <col min="4" max="4" width="18.6328125" customWidth="1"/>
     <col min="5" max="5" width="22.90625" customWidth="1"/>
     <col min="6" max="6" width="17.453125" customWidth="1"/>
     <col min="7" max="7" width="18.81640625" customWidth="1"/>
@@ -566,22 +531,22 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/user/user.xlsx
+++ b/data/user/user.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6092218aa314deb/Dokumente/hackerthon/data/user/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{C74F6FAA-9F9A-4FC4-BE34-46D1A99E7820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A8916C7-DDB8-427A-9FB0-49682C48C13B}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{C74F6FAA-9F9A-4FC4-BE34-46D1A99E7820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D0DF736-88A2-42DD-84A1-A9C2A5B61267}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" activeTab="1" xr2:uid="{D427C77A-E679-44B6-86BB-64B55F7FE4CF}"/>
   </bookViews>
@@ -40,13 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
-  <si>
-    <t>user_name</t>
-  </si>
-  <si>
-    <t>user_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>password</t>
   </si>
@@ -57,12 +51,6 @@
     <t>phone</t>
   </si>
   <si>
-    <t>contry</t>
-  </si>
-  <si>
-    <t>sessionid</t>
-  </si>
-  <si>
     <t>health_float</t>
   </si>
   <si>
@@ -79,6 +67,15 @@
   </si>
   <si>
     <t>gen_profile</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>most_significant_problem</t>
   </si>
 </sst>
 </file>
@@ -474,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF23E60B-A837-445F-A5D3-97DFECDC65C9}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="13.7265625" customWidth="1"/>
@@ -482,30 +479,24 @@
     <col min="6" max="6" width="12.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E2" s="1"/>
     </row>
   </sheetData>
@@ -515,7 +506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B514BF7-5519-47A1-8F28-4F0F2112BDC4}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -524,28 +515,32 @@
     <col min="5" max="5" width="22.90625" customWidth="1"/>
     <col min="6" max="6" width="17.453125" customWidth="1"/>
     <col min="7" max="7" width="18.81640625" customWidth="1"/>
+    <col min="8" max="8" width="21.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>11</v>
       </c>
     </row>
